--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2483"/>
+  <dimension ref="A1:I2484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72460,6 +72460,35 @@
       </c>
       <c r="I2483" t="n">
         <v>4329606</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2484" t="n">
+        <v>3204468</v>
+      </c>
+      <c r="C2484" t="n">
+        <v>2517175</v>
+      </c>
+      <c r="D2484" t="n">
+        <v>687293</v>
+      </c>
+      <c r="E2484" t="n">
+        <v>2931225</v>
+      </c>
+      <c r="F2484" t="n">
+        <v>161683</v>
+      </c>
+      <c r="G2484" t="n">
+        <v>110356</v>
+      </c>
+      <c r="H2484" t="n">
+        <v>1204</v>
+      </c>
+      <c r="I2484" t="n">
+        <v>2245139</v>
       </c>
     </row>
   </sheetData>
@@ -72520,7 +72549,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2020.csv https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2021.csv https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2022.csv https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2023.csv https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2024.csv https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2025.csv https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2026.csv</t>
+          <t>https://archivos-datos.transporte.gob.ar/upload/Dat_Ab_Usos/dat-ab-usos-2026.csv</t>
         </is>
       </c>
     </row>
@@ -72532,7 +72561,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T20:30:21Z</t>
+          <t>2026-10-20T18:08:31Z</t>
         </is>
       </c>
     </row>
@@ -72544,7 +72573,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2484"/>
+  <dimension ref="A1:I2485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72489,6 +72489,35 @@
       </c>
       <c r="I2484" t="n">
         <v>2245139</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2485" t="n">
+        <v>11964727</v>
+      </c>
+      <c r="C2485" t="n">
+        <v>9025421</v>
+      </c>
+      <c r="D2485" t="n">
+        <v>2939306</v>
+      </c>
+      <c r="E2485" t="n">
+        <v>10631018</v>
+      </c>
+      <c r="F2485" t="n">
+        <v>875316</v>
+      </c>
+      <c r="G2485" t="n">
+        <v>457101</v>
+      </c>
+      <c r="H2485" t="n">
+        <v>1292</v>
+      </c>
+      <c r="I2485" t="n">
+        <v>7693867</v>
       </c>
     </row>
   </sheetData>
@@ -72561,7 +72590,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T18:08:31Z</t>
+          <t>2026-10-21T12:53:13Z</t>
         </is>
       </c>
     </row>
@@ -72573,7 +72602,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2485"/>
+  <dimension ref="A1:I2486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72518,6 +72518,35 @@
       </c>
       <c r="I2485" t="n">
         <v>7693867</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2486" t="n">
+        <v>12452182</v>
+      </c>
+      <c r="C2486" t="n">
+        <v>9371785</v>
+      </c>
+      <c r="D2486" t="n">
+        <v>3080397</v>
+      </c>
+      <c r="E2486" t="n">
+        <v>11247291</v>
+      </c>
+      <c r="F2486" t="n">
+        <v>923051</v>
+      </c>
+      <c r="G2486" t="n">
+        <v>280498</v>
+      </c>
+      <c r="H2486" t="n">
+        <v>1342</v>
+      </c>
+      <c r="I2486" t="n">
+        <v>8169659</v>
       </c>
     </row>
   </sheetData>
@@ -72590,7 +72619,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21T12:53:13Z</t>
+          <t>2026-10-22T09:28:33Z</t>
         </is>
       </c>
     </row>
@@ -72602,7 +72631,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2486"/>
+  <dimension ref="A1:I2487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72547,6 +72547,35 @@
       </c>
       <c r="I2486" t="n">
         <v>8169659</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2487" t="n">
+        <v>11987231</v>
+      </c>
+      <c r="C2487" t="n">
+        <v>8932671</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>3054560</v>
+      </c>
+      <c r="E2487" t="n">
+        <v>10596286</v>
+      </c>
+      <c r="F2487" t="n">
+        <v>903083</v>
+      </c>
+      <c r="G2487" t="n">
+        <v>486626</v>
+      </c>
+      <c r="H2487" t="n">
+        <v>1236</v>
+      </c>
+      <c r="I2487" t="n">
+        <v>7544480</v>
       </c>
     </row>
   </sheetData>
@@ -72619,7 +72648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:28:33Z</t>
+          <t>2026-10-23T09:24:48Z</t>
         </is>
       </c>
     </row>
@@ -72631,7 +72660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2487"/>
+  <dimension ref="A1:I2488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72576,6 +72576,35 @@
       </c>
       <c r="I2487" t="n">
         <v>7544480</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>11485753</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>8627244</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>2858509</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>10143276</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>868036</v>
+      </c>
+      <c r="G2488" t="n">
+        <v>473191</v>
+      </c>
+      <c r="H2488" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I2488" t="n">
+        <v>7287227</v>
       </c>
     </row>
   </sheetData>
@@ -72648,7 +72677,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:24:48Z</t>
+          <t>2026-10-24T08:56:14Z</t>
         </is>
       </c>
     </row>
@@ -72660,7 +72689,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2488"/>
+  <dimension ref="A1:I2489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72605,6 +72605,35 @@
       </c>
       <c r="I2488" t="n">
         <v>7287227</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>12055108</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>9180398</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>2874710</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>10703464</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>888577</v>
+      </c>
+      <c r="G2489" t="n">
+        <v>461578</v>
+      </c>
+      <c r="H2489" t="n">
+        <v>1489</v>
+      </c>
+      <c r="I2489" t="n">
+        <v>7831046</v>
       </c>
     </row>
   </sheetData>
@@ -72677,7 +72706,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:56:14Z</t>
+          <t>2026-10-25T09:13:05Z</t>
         </is>
       </c>
     </row>
@@ -72689,7 +72718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2489"/>
+  <dimension ref="A1:I2490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72634,6 +72634,35 @@
       </c>
       <c r="I2489" t="n">
         <v>7831046</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>5851314</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>4716587</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>1134727</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>5201652</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>428400</v>
+      </c>
+      <c r="G2490" t="n">
+        <v>219840</v>
+      </c>
+      <c r="H2490" t="n">
+        <v>1422</v>
+      </c>
+      <c r="I2490" t="n">
+        <v>4068352</v>
       </c>
     </row>
   </sheetData>
@@ -72706,7 +72735,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:13:05Z</t>
+          <t>2026-10-26T10:15:06Z</t>
         </is>
       </c>
     </row>
@@ -72718,7 +72747,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2490"/>
+  <dimension ref="A1:I2491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72663,6 +72663,35 @@
       </c>
       <c r="I2490" t="n">
         <v>4068352</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>3144614</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>2501132</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>643482</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>2879327</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>140108</v>
+      </c>
+      <c r="G2491" t="n">
+        <v>124315</v>
+      </c>
+      <c r="H2491" t="n">
+        <v>864</v>
+      </c>
+      <c r="I2491" t="n">
+        <v>2236718</v>
       </c>
     </row>
   </sheetData>
@@ -72735,7 +72764,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:15:06Z</t>
+          <t>2026-10-27T09:52:25Z</t>
         </is>
       </c>
     </row>
@@ -72747,7 +72776,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2491"/>
+  <dimension ref="A1:I2492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72692,6 +72692,35 @@
       </c>
       <c r="I2491" t="n">
         <v>2236718</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>12298613</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>9252996</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>3045617</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>10937954</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>899505</v>
+      </c>
+      <c r="G2492" t="n">
+        <v>459879</v>
+      </c>
+      <c r="H2492" t="n">
+        <v>1275</v>
+      </c>
+      <c r="I2492" t="n">
+        <v>7894269</v>
       </c>
     </row>
   </sheetData>
@@ -72764,7 +72793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:52:25Z</t>
+          <t>2026-10-28T10:39:31Z</t>
         </is>
       </c>
     </row>
@@ -72776,7 +72805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2492"/>
+  <dimension ref="A1:I2493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72721,6 +72721,35 @@
       </c>
       <c r="I2492" t="n">
         <v>7894269</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>12305823</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>9274633</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>3031190</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>10915874</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>906352</v>
+      </c>
+      <c r="G2493" t="n">
+        <v>482386</v>
+      </c>
+      <c r="H2493" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I2493" t="n">
+        <v>7887344</v>
       </c>
     </row>
   </sheetData>
@@ -72793,7 +72822,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:39:31Z</t>
+          <t>2026-10-29T10:57:12Z</t>
         </is>
       </c>
     </row>
@@ -72805,7 +72834,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2493"/>
+  <dimension ref="A1:I2494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72750,6 +72750,35 @@
       </c>
       <c r="I2493" t="n">
         <v>7887344</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>12140210</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>9169297</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>2970913</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>10762781</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>897425</v>
+      </c>
+      <c r="G2494" t="n">
+        <v>478733</v>
+      </c>
+      <c r="H2494" t="n">
+        <v>1271</v>
+      </c>
+      <c r="I2494" t="n">
+        <v>7794593</v>
       </c>
     </row>
   </sheetData>
@@ -72822,7 +72851,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:57:12Z</t>
+          <t>2026-10-30T10:55:00Z</t>
         </is>
       </c>
     </row>
@@ -72834,7 +72863,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube.xlsx
+++ b/data/excel/sube.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2494"/>
+  <dimension ref="A1:I2495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72779,6 +72779,35 @@
       </c>
       <c r="I2494" t="n">
         <v>7794593</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>11184380</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>8486102</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>2698278</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>9829711</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>889354</v>
+      </c>
+      <c r="G2495" t="n">
+        <v>464134</v>
+      </c>
+      <c r="H2495" t="n">
+        <v>1181</v>
+      </c>
+      <c r="I2495" t="n">
+        <v>7133908</v>
       </c>
     </row>
   </sheetData>
@@ -72851,7 +72880,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:55:00Z</t>
+          <t>2026-10-31T10:27:05Z</t>
         </is>
       </c>
     </row>
@@ -72863,7 +72892,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
